--- a/survey_templates/013_teen_screen_time_survey--survey_templates.xlsx
+++ b/survey_templates/013_teen_screen_time_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1976,17 +1976,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>survey_parent_conversation_choices</t>
+          <t>survey_parent_screen_time_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>almost_every_time</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Almost every time</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2015,46 +2015,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>almost_every_time</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Almost every time</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>survey_parent_screen_time_choices</t>
+          <t>survey_parent_rules_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>almost_every_time</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Almost every time</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>survey_parent_screen_time_choices</t>
+          <t>survey_parent_rules_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>almost_every_time</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Almost every time</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2066,46 +2066,46 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes,_partially</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes, partially</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>survey_parent_rules_choices</t>
+          <t>survey_parent_monitoring_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>survey_parent_rules_choices</t>
+          <t>survey_parent_monitoring_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>yes,_partially</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes, partially</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2117,46 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>survey_parent_monitoring_choices</t>
+          <t>survey_parent_approve_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>survey_parent_monitoring_choices</t>
+          <t>survey_parent_approve_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2168,46 +2168,46 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes,_partially</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes, partially</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>survey_parent_approve_choices</t>
+          <t>survey_parent_screen_time_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>survey_parent_approve_choices</t>
+          <t>survey_parent_screen_time_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>yes,_partially</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes, partially</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>less_than_1_hour</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Less than 1 hour</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1-2_hours</t>
+          <t>4-6_hours</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1-2 hours</t>
+          <t>4-6 hours</t>
         </is>
       </c>
     </row>
@@ -2253,46 +2253,46 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2-4_hours</t>
+          <t>more_than_6_hours</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2-4 hours</t>
+          <t>More than 6 hours</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>survey_parent_screen_time_choices</t>
+          <t>survey_screening_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>4-6_hours</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4-6 hours</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>survey_parent_screen_time_choices</t>
+          <t>survey_screening_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>more_than_6_hours</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>More than 6 hours</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -2304,80 +2304,80 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>survey_screening_choices</t>
+          <t>survey_screen_time_limit_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>survey_screening_choices</t>
+          <t>survey_screen_time_limit_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>survey_screen_time_limit_choices</t>
+          <t>survey_screening_time_limit_reason_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>to_protect_eyes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>To protect eyes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>survey_screen_time_limit_choices</t>
+          <t>survey_screening_time_limit_reason_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>to_avoid_addiction</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>To avoid addiction</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>to_protect_eyes</t>
+          <t>to_prevent_social_comparison</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>To protect eyes</t>
+          <t>To prevent social comparison</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>to_avoid_addiction</t>
+          <t>to_prevent_cyberbullying</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>To avoid addiction</t>
+          <t>To prevent cyberbullying</t>
         </is>
       </c>
     </row>
@@ -2423,46 +2423,46 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>to_prevent_social_comparison</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>To prevent social comparison</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>survey_screening_time_limit_reason_choices</t>
+          <t>survey_screen_time_limit_type_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>to_prevent_cyberbullying</t>
+          <t>time_limit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>To prevent cyberbullying</t>
+          <t>Time limit</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>survey_screening_time_limit_reason_choices</t>
+          <t>survey_screen_time_limit_type_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>content_filter</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Content filter</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>time_limit</t>
+          <t>app_limit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Time limit</t>
+          <t>App limit</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>content_filter</t>
+          <t>device_limit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Content filter</t>
+          <t>Device limit</t>
         </is>
       </c>
     </row>
@@ -2508,44 +2508,10 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>app_limit</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
-        <is>
-          <t>App limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>survey_screen_time_limit_type_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>device_limit</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Device limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>survey_screen_time_limit_type_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>other_(please_specify)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
         <is>
           <t>Other (please specify)</t>
         </is>
